--- a/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
+++ b/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="10860" windowHeight="8400"/>
   </bookViews>
   <sheets>
-    <sheet name="Signin page" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -28,24 +28,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
-    <t>FieldName</t>
+    <t>UserName</t>
   </si>
   <si>
-    <t>Email</t>
+    <t>Password</t>
   </si>
   <si>
-    <t>Valid_Password</t>
+    <t>ExpectedResults</t>
   </si>
   <si>
-    <t>Invalid_Password</t>
+    <t>scarlevga81@gmail.com</t>
   </si>
   <si>
-    <t>Rule_pssword</t>
+    <t>SZDLMA24j</t>
   </si>
   <si>
-    <t>valid format</t>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>52664356Trox!!</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>jamalselowa@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -684,14 +693,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1219,35 +1234,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>4</v>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="scarlevga81@gmail.com"/>
+    <hyperlink ref="A3" r:id="rId1" display="scarlevga81@gmail.com"/>
+    <hyperlink ref="A4" r:id="rId2" display="jamalselowa@gmail.com"/>
+    <hyperlink ref="A5" r:id="rId2" display="jamalselowa@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1256,17 +1308,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>5</v>
+      <c r="C1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
+++ b/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10860" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>UserName</t>
   </si>
   <si>
     <t>Password</t>
-  </si>
-  <si>
-    <t>ExpectedResults</t>
   </si>
   <si>
     <t>scarlevga81@gmail.com</t>
@@ -45,13 +42,7 @@
     <t>SZDLMA24j</t>
   </si>
   <si>
-    <t>Valid</t>
-  </si>
-  <si>
     <t>52664356Trox!!</t>
-  </si>
-  <si>
-    <t>Invalid</t>
   </si>
   <si>
     <t>jamalselowa@gmail.com</t>
@@ -1241,56 +1232,43 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
+++ b/selenium-framework/target/test-classes/com/automation/Resources/Configurations/Test-Data/Test_Data_Fields_Verification.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="8400" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Registeration" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>UserName</t>
   </si>
@@ -46,6 +46,30 @@
   </si>
   <si>
     <t>jamalselowa@gmail.com</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>John_Smith</t>
+  </si>
+  <si>
+    <t>john@test.com</t>
+  </si>
+  <si>
+    <t>Test123</t>
+  </si>
+  <si>
+    <t>Marry_Vega</t>
+  </si>
+  <si>
+    <t>mary@@test.com</t>
+  </si>
+  <si>
+    <t>26@Mary</t>
   </si>
 </sst>
 </file>
@@ -688,16 +712,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,18 +1253,18 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -1248,7 +1272,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1256,7 +1280,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
@@ -1264,7 +1288,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
@@ -1286,18 +1310,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="john@test.com"/>
+    <hyperlink ref="B3" r:id="rId2" display="mary@@test.com"/>
+    <hyperlink ref="C3" r:id="rId3" display="26@Mary"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
